--- a/AAII_Financials/Quarterly/GTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -758,25 +758,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>89800</v>
+        <v>90500</v>
       </c>
       <c r="E8" s="3">
-        <v>19000</v>
+        <v>19100</v>
       </c>
       <c r="F8" s="3">
-        <v>15200</v>
+        <v>15300</v>
       </c>
       <c r="G8" s="3">
-        <v>20300</v>
+        <v>20400</v>
       </c>
       <c r="H8" s="3">
-        <v>21100</v>
+        <v>21200</v>
       </c>
       <c r="I8" s="3">
-        <v>19400</v>
+        <v>19500</v>
       </c>
       <c r="J8" s="3">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="K8" s="3">
         <v>19000</v>
@@ -823,19 +823,19 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>51000</v>
+        <v>51300</v>
       </c>
       <c r="E9" s="3">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="F9" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="G9" s="3">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="H9" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="I9" s="3">
         <v>6400</v>
@@ -888,10 +888,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>38900</v>
+        <v>39100</v>
       </c>
       <c r="E10" s="3">
-        <v>7700</v>
+        <v>7800</v>
       </c>
       <c r="F10" s="3">
         <v>8500</v>
@@ -900,13 +900,13 @@
         <v>11600</v>
       </c>
       <c r="H10" s="3">
-        <v>14500</v>
+        <v>14600</v>
       </c>
       <c r="I10" s="3">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="J10" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="K10" s="3">
         <v>12000</v>
@@ -978,19 +978,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>40100</v>
+        <v>40400</v>
       </c>
       <c r="E12" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="F12" s="3">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="G12" s="3">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="H12" s="3">
-        <v>8600</v>
+        <v>8700</v>
       </c>
       <c r="I12" s="3">
         <v>7800</v>
@@ -1260,25 +1260,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>186800</v>
+        <v>188100</v>
       </c>
       <c r="E17" s="3">
-        <v>42500</v>
+        <v>42800</v>
       </c>
       <c r="F17" s="3">
-        <v>40100</v>
+        <v>40300</v>
       </c>
       <c r="G17" s="3">
-        <v>45700</v>
+        <v>46000</v>
       </c>
       <c r="H17" s="3">
-        <v>38300</v>
+        <v>38600</v>
       </c>
       <c r="I17" s="3">
-        <v>33200</v>
+        <v>33500</v>
       </c>
       <c r="J17" s="3">
-        <v>27800</v>
+        <v>28000</v>
       </c>
       <c r="K17" s="3">
         <v>31700</v>
@@ -1325,25 +1325,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-96900</v>
+        <v>-97600</v>
       </c>
       <c r="E18" s="3">
-        <v>-23500</v>
+        <v>-23700</v>
       </c>
       <c r="F18" s="3">
-        <v>-24800</v>
+        <v>-25000</v>
       </c>
       <c r="G18" s="3">
-        <v>-25400</v>
+        <v>-25600</v>
       </c>
       <c r="H18" s="3">
-        <v>-17200</v>
+        <v>-17400</v>
       </c>
       <c r="I18" s="3">
-        <v>-13800</v>
+        <v>-13900</v>
       </c>
       <c r="J18" s="3">
-        <v>-15000</v>
+        <v>-15100</v>
       </c>
       <c r="K18" s="3">
         <v>-12600</v>
@@ -1415,10 +1415,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-15000</v>
+        <v>-15100</v>
       </c>
       <c r="E20" s="3">
-        <v>-9100</v>
+        <v>-9200</v>
       </c>
       <c r="F20" s="3">
         <v>700</v>
@@ -1610,25 +1610,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-111900</v>
+        <v>-112700</v>
       </c>
       <c r="E23" s="3">
-        <v>-32600</v>
+        <v>-32800</v>
       </c>
       <c r="F23" s="3">
-        <v>-24100</v>
+        <v>-24300</v>
       </c>
       <c r="G23" s="3">
-        <v>-22800</v>
+        <v>-23000</v>
       </c>
       <c r="H23" s="3">
-        <v>-18000</v>
+        <v>-18100</v>
       </c>
       <c r="I23" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="J23" s="3">
-        <v>-15900</v>
+        <v>-16000</v>
       </c>
       <c r="K23" s="3">
         <v>-10400</v>
@@ -1805,25 +1805,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-111900</v>
+        <v>-112700</v>
       </c>
       <c r="E26" s="3">
-        <v>-32600</v>
+        <v>-32800</v>
       </c>
       <c r="F26" s="3">
-        <v>-24100</v>
+        <v>-24300</v>
       </c>
       <c r="G26" s="3">
-        <v>-22800</v>
+        <v>-23000</v>
       </c>
       <c r="H26" s="3">
-        <v>-18000</v>
+        <v>-18100</v>
       </c>
       <c r="I26" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="J26" s="3">
-        <v>-15900</v>
+        <v>-16000</v>
       </c>
       <c r="K26" s="3">
         <v>-10400</v>
@@ -1870,25 +1870,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-111600</v>
+        <v>-112400</v>
       </c>
       <c r="E27" s="3">
-        <v>-32500</v>
+        <v>-32700</v>
       </c>
       <c r="F27" s="3">
-        <v>-24100</v>
+        <v>-24200</v>
       </c>
       <c r="G27" s="3">
-        <v>-22500</v>
+        <v>-22600</v>
       </c>
       <c r="H27" s="3">
-        <v>-17800</v>
+        <v>-17900</v>
       </c>
       <c r="I27" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="J27" s="3">
-        <v>-15600</v>
+        <v>-15700</v>
       </c>
       <c r="K27" s="3">
         <v>-10400</v>
@@ -2195,10 +2195,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="E32" s="3">
-        <v>9100</v>
+        <v>9200</v>
       </c>
       <c r="F32" s="3">
         <v>-700</v>
@@ -2260,25 +2260,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-111600</v>
+        <v>-112400</v>
       </c>
       <c r="E33" s="3">
-        <v>-32500</v>
+        <v>-32700</v>
       </c>
       <c r="F33" s="3">
-        <v>-24100</v>
+        <v>-24200</v>
       </c>
       <c r="G33" s="3">
-        <v>-22500</v>
+        <v>-22600</v>
       </c>
       <c r="H33" s="3">
-        <v>-17800</v>
+        <v>-17900</v>
       </c>
       <c r="I33" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="J33" s="3">
-        <v>-15600</v>
+        <v>-15700</v>
       </c>
       <c r="K33" s="3">
         <v>-10400</v>
@@ -2390,25 +2390,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-111600</v>
+        <v>-112400</v>
       </c>
       <c r="E35" s="3">
-        <v>-32500</v>
+        <v>-32700</v>
       </c>
       <c r="F35" s="3">
-        <v>-24100</v>
+        <v>-24200</v>
       </c>
       <c r="G35" s="3">
-        <v>-22500</v>
+        <v>-22600</v>
       </c>
       <c r="H35" s="3">
-        <v>-17800</v>
+        <v>-17900</v>
       </c>
       <c r="I35" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="J35" s="3">
-        <v>-15600</v>
+        <v>-15700</v>
       </c>
       <c r="K35" s="3">
         <v>-10400</v>
@@ -2575,25 +2575,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>24300</v>
+        <v>24500</v>
       </c>
       <c r="E41" s="3">
-        <v>45200</v>
+        <v>45500</v>
       </c>
       <c r="F41" s="3">
-        <v>44100</v>
+        <v>44400</v>
       </c>
       <c r="G41" s="3">
-        <v>88200</v>
+        <v>88800</v>
       </c>
       <c r="H41" s="3">
-        <v>112600</v>
+        <v>113300</v>
       </c>
       <c r="I41" s="3">
-        <v>147300</v>
+        <v>148300</v>
       </c>
       <c r="J41" s="3">
-        <v>147600</v>
+        <v>148600</v>
       </c>
       <c r="K41" s="3">
         <v>195600</v>
@@ -2640,25 +2640,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>21700</v>
+        <v>21900</v>
       </c>
       <c r="E42" s="3">
-        <v>20000</v>
+        <v>20200</v>
       </c>
       <c r="F42" s="3">
-        <v>33100</v>
+        <v>33300</v>
       </c>
       <c r="G42" s="3">
-        <v>20900</v>
+        <v>21100</v>
       </c>
       <c r="H42" s="3">
-        <v>25900</v>
+        <v>26100</v>
       </c>
       <c r="I42" s="3">
-        <v>19600</v>
+        <v>19800</v>
       </c>
       <c r="J42" s="3">
-        <v>44000</v>
+        <v>44300</v>
       </c>
       <c r="K42" s="3">
         <v>19900</v>
@@ -2705,25 +2705,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>44600</v>
+        <v>45000</v>
       </c>
       <c r="E43" s="3">
-        <v>59700</v>
+        <v>60100</v>
       </c>
       <c r="F43" s="3">
-        <v>56100</v>
+        <v>56500</v>
       </c>
       <c r="G43" s="3">
-        <v>53600</v>
+        <v>54000</v>
       </c>
       <c r="H43" s="3">
-        <v>50500</v>
+        <v>50800</v>
       </c>
       <c r="I43" s="3">
-        <v>36100</v>
+        <v>36300</v>
       </c>
       <c r="J43" s="3">
-        <v>30900</v>
+        <v>31200</v>
       </c>
       <c r="K43" s="3">
         <v>29600</v>
@@ -2776,7 +2776,7 @@
         <v>7600</v>
       </c>
       <c r="F44" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="G44" s="3">
         <v>4900</v>
@@ -2838,16 +2838,16 @@
         <v>1300</v>
       </c>
       <c r="E45" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="F45" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="3">
         <v>4500</v>
       </c>
       <c r="H45" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="I45" s="3">
         <v>5100</v>
@@ -2900,25 +2900,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>97900</v>
+        <v>98600</v>
       </c>
       <c r="E46" s="3">
-        <v>136700</v>
+        <v>137600</v>
       </c>
       <c r="F46" s="3">
-        <v>144200</v>
+        <v>145200</v>
       </c>
       <c r="G46" s="3">
-        <v>172200</v>
+        <v>173400</v>
       </c>
       <c r="H46" s="3">
-        <v>198800</v>
+        <v>200200</v>
       </c>
       <c r="I46" s="3">
-        <v>212700</v>
+        <v>214100</v>
       </c>
       <c r="J46" s="3">
-        <v>231500</v>
+        <v>233100</v>
       </c>
       <c r="K46" s="3">
         <v>253900</v>
@@ -2971,7 +2971,7 @@
         <v>6800</v>
       </c>
       <c r="F47" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="G47" s="3">
         <v>6900</v>
@@ -2980,7 +2980,7 @@
         <v>5100</v>
       </c>
       <c r="I47" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="J47" s="3">
         <v>4600</v>
@@ -3030,25 +3030,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>24500</v>
+        <v>24700</v>
       </c>
       <c r="E48" s="3">
-        <v>28300</v>
+        <v>28500</v>
       </c>
       <c r="F48" s="3">
-        <v>24800</v>
+        <v>25000</v>
       </c>
       <c r="G48" s="3">
-        <v>22400</v>
+        <v>22600</v>
       </c>
       <c r="H48" s="3">
-        <v>18800</v>
+        <v>19000</v>
       </c>
       <c r="I48" s="3">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="J48" s="3">
-        <v>18500</v>
+        <v>18700</v>
       </c>
       <c r="K48" s="3">
         <v>19400</v>
@@ -3095,7 +3095,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="E49" s="3">
         <v>3900</v>
@@ -3293,7 +3293,7 @@
         <v>900</v>
       </c>
       <c r="E52" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="F52" s="3">
         <v>4300</v>
@@ -3305,7 +3305,7 @@
         <v>3300</v>
       </c>
       <c r="I52" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="J52" s="3">
         <v>3600</v>
@@ -3420,25 +3420,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>134700</v>
+        <v>135600</v>
       </c>
       <c r="E54" s="3">
-        <v>180000</v>
+        <v>181200</v>
       </c>
       <c r="F54" s="3">
-        <v>183500</v>
+        <v>184700</v>
       </c>
       <c r="G54" s="3">
-        <v>209600</v>
+        <v>211000</v>
       </c>
       <c r="H54" s="3">
-        <v>228100</v>
+        <v>229700</v>
       </c>
       <c r="I54" s="3">
-        <v>241300</v>
+        <v>242900</v>
       </c>
       <c r="J54" s="3">
-        <v>260100</v>
+        <v>261900</v>
       </c>
       <c r="K54" s="3">
         <v>280000</v>
@@ -3535,25 +3535,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>34400</v>
+        <v>34600</v>
       </c>
       <c r="E57" s="3">
-        <v>29100</v>
+        <v>29300</v>
       </c>
       <c r="F57" s="3">
-        <v>25900</v>
+        <v>26100</v>
       </c>
       <c r="G57" s="3">
-        <v>29400</v>
+        <v>29600</v>
       </c>
       <c r="H57" s="3">
-        <v>21900</v>
+        <v>22000</v>
       </c>
       <c r="I57" s="3">
-        <v>19900</v>
+        <v>20000</v>
       </c>
       <c r="J57" s="3">
-        <v>22500</v>
+        <v>22600</v>
       </c>
       <c r="K57" s="3">
         <v>20600</v>
@@ -3600,25 +3600,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18100</v>
+        <v>18200</v>
       </c>
       <c r="E58" s="3">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="F58" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="G58" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="H58" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="I58" s="3">
         <v>6500</v>
       </c>
       <c r="J58" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="K58" s="3">
         <v>10700</v>
@@ -3730,25 +3730,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>53800</v>
+        <v>54200</v>
       </c>
       <c r="E60" s="3">
-        <v>48300</v>
+        <v>48700</v>
       </c>
       <c r="F60" s="3">
-        <v>34500</v>
+        <v>34700</v>
       </c>
       <c r="G60" s="3">
-        <v>36600</v>
+        <v>36900</v>
       </c>
       <c r="H60" s="3">
-        <v>30400</v>
+        <v>30600</v>
       </c>
       <c r="I60" s="3">
-        <v>28400</v>
+        <v>28500</v>
       </c>
       <c r="J60" s="3">
-        <v>31500</v>
+        <v>31700</v>
       </c>
       <c r="K60" s="3">
         <v>32500</v>
@@ -3813,7 +3813,7 @@
         <v>5600</v>
       </c>
       <c r="J61" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="K61" s="3">
         <v>6900</v>
@@ -3860,7 +3860,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E62" s="3">
         <v>1300</v>
@@ -4120,25 +4120,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>59300</v>
+        <v>59700</v>
       </c>
       <c r="E66" s="3">
-        <v>56800</v>
+        <v>57200</v>
       </c>
       <c r="F66" s="3">
-        <v>40400</v>
+        <v>40700</v>
       </c>
       <c r="G66" s="3">
-        <v>43100</v>
+        <v>43400</v>
       </c>
       <c r="H66" s="3">
-        <v>37000</v>
+        <v>37300</v>
       </c>
       <c r="I66" s="3">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="J66" s="3">
-        <v>40100</v>
+        <v>40300</v>
       </c>
       <c r="K66" s="3">
         <v>39400</v>
@@ -4470,25 +4470,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-854600</v>
+        <v>-860400</v>
       </c>
       <c r="E72" s="3">
-        <v>-804400</v>
+        <v>-809900</v>
       </c>
       <c r="F72" s="3">
-        <v>-783600</v>
+        <v>-789000</v>
       </c>
       <c r="G72" s="3">
-        <v>-760200</v>
+        <v>-765400</v>
       </c>
       <c r="H72" s="3">
-        <v>-734400</v>
+        <v>-739400</v>
       </c>
       <c r="I72" s="3">
-        <v>-717300</v>
+        <v>-722200</v>
       </c>
       <c r="J72" s="3">
-        <v>-700700</v>
+        <v>-705400</v>
       </c>
       <c r="K72" s="3">
         <v>-705800</v>
@@ -4730,25 +4730,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>75400</v>
+        <v>75900</v>
       </c>
       <c r="E76" s="3">
-        <v>123200</v>
+        <v>124000</v>
       </c>
       <c r="F76" s="3">
-        <v>143100</v>
+        <v>144000</v>
       </c>
       <c r="G76" s="3">
-        <v>166500</v>
+        <v>167600</v>
       </c>
       <c r="H76" s="3">
-        <v>191100</v>
+        <v>192400</v>
       </c>
       <c r="I76" s="3">
-        <v>205100</v>
+        <v>206500</v>
       </c>
       <c r="J76" s="3">
-        <v>220100</v>
+        <v>221600</v>
       </c>
       <c r="K76" s="3">
         <v>240600</v>
@@ -4930,25 +4930,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-111600</v>
+        <v>-112400</v>
       </c>
       <c r="E81" s="3">
-        <v>-32500</v>
+        <v>-32700</v>
       </c>
       <c r="F81" s="3">
-        <v>-24100</v>
+        <v>-24200</v>
       </c>
       <c r="G81" s="3">
-        <v>-22500</v>
+        <v>-22600</v>
       </c>
       <c r="H81" s="3">
-        <v>-17800</v>
+        <v>-17900</v>
       </c>
       <c r="I81" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="J81" s="3">
-        <v>-15600</v>
+        <v>-15700</v>
       </c>
       <c r="K81" s="3">
         <v>-10400</v>
